--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>124.73675</v>
+        <v>16.96339</v>
       </c>
       <c r="D2" t="n">
-        <v>86.24263000000001</v>
+        <v>16.57194</v>
       </c>
       <c r="E2" t="n">
-        <v>91.81025</v>
+        <v>16.76488</v>
       </c>
       <c r="F2" t="n">
-        <v>525.42252</v>
+        <v>42.97086</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05127</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.83575</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>125.72171</v>
+        <v>17.15668</v>
       </c>
       <c r="D3" t="n">
-        <v>87.12025</v>
+        <v>16.9154</v>
       </c>
       <c r="E3" t="n">
-        <v>91.25162</v>
+        <v>17.11128</v>
       </c>
       <c r="F3" t="n">
-        <v>525.43912</v>
+        <v>42.96509</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05139</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.82591</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>123.50008</v>
+        <v>17.10184</v>
       </c>
       <c r="D4" t="n">
-        <v>86.46366999999999</v>
+        <v>16.78397</v>
       </c>
       <c r="E4" t="n">
-        <v>93.21716000000001</v>
+        <v>16.99093</v>
       </c>
       <c r="F4" t="n">
-        <v>531.55063</v>
+        <v>43.09774</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05104</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.84353</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121.15085</v>
+        <v>17.16475</v>
       </c>
       <c r="D5" t="n">
-        <v>85.49267999999999</v>
+        <v>16.45221</v>
       </c>
       <c r="E5" t="n">
-        <v>92.22794</v>
+        <v>17.10036</v>
       </c>
       <c r="F5" t="n">
-        <v>528.75166</v>
+        <v>43.14545</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.82908</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>123.88539</v>
+        <v>17.11729</v>
       </c>
       <c r="D6" t="n">
-        <v>87.94517999999999</v>
+        <v>16.13842</v>
       </c>
       <c r="E6" t="n">
-        <v>92.44555</v>
+        <v>16.97509</v>
       </c>
       <c r="F6" t="n">
-        <v>527.03315</v>
+        <v>43.1686</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05214</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83543</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>120.14494</v>
+        <v>17.26687</v>
       </c>
       <c r="D7" t="n">
-        <v>86.85554</v>
+        <v>16.81449</v>
       </c>
       <c r="E7" t="n">
-        <v>91.89357</v>
+        <v>16.99709</v>
       </c>
       <c r="F7" t="n">
-        <v>530.80596</v>
+        <v>42.81834</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.8791</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>125.04073</v>
+        <v>16.99079</v>
       </c>
       <c r="D8" t="n">
-        <v>86.27134</v>
+        <v>16.95272</v>
       </c>
       <c r="E8" t="n">
-        <v>93.21862</v>
+        <v>16.97904</v>
       </c>
       <c r="F8" t="n">
-        <v>518.34403</v>
+        <v>43.27637</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.82306</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>123.02832</v>
+        <v>17.00344</v>
       </c>
       <c r="D9" t="n">
-        <v>87.39581</v>
+        <v>16.73846</v>
       </c>
       <c r="E9" t="n">
-        <v>91.87508</v>
+        <v>16.75051</v>
       </c>
       <c r="F9" t="n">
-        <v>521.78117</v>
+        <v>43.57931</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.87441</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>123.68915</v>
+        <v>16.87064</v>
       </c>
       <c r="D10" t="n">
-        <v>85.34026</v>
+        <v>16.75554</v>
       </c>
       <c r="E10" t="n">
-        <v>93.1619</v>
+        <v>16.76744</v>
       </c>
       <c r="F10" t="n">
-        <v>517.07692</v>
+        <v>43.66639</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.81121</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.71166</v>
+        <v>16.96778</v>
       </c>
       <c r="D12" t="n">
-        <v>24.67088</v>
+        <v>16.84748</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.85881</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.19017</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81949</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.76206</v>
+        <v>17.19279</v>
       </c>
       <c r="D13" t="n">
-        <v>25.2594</v>
+        <v>16.94621</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.09505</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.17997</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05156</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.81568</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.76877</v>
+        <v>17.05781</v>
       </c>
       <c r="D14" t="n">
-        <v>24.56716</v>
+        <v>16.8604</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.01498</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.88208</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05102</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.83849</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.793139999999999</v>
+        <v>17.19314</v>
       </c>
       <c r="D15" t="n">
-        <v>24.51646</v>
+        <v>16.72872</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.01455</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.09737</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84604</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.76153</v>
+        <v>17.01485</v>
       </c>
       <c r="D16" t="n">
-        <v>24.60355</v>
+        <v>16.60825</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.92903</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.40194</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.81005</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.64002</v>
+        <v>17.04708</v>
       </c>
       <c r="D17" t="n">
-        <v>25.1987</v>
+        <v>16.52787</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.84354</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.66348</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.81843</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.752750000000001</v>
+        <v>16.90723</v>
       </c>
       <c r="D18" t="n">
-        <v>24.46905</v>
+        <v>16.68168</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.89205</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.00811</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.8868</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.71613</v>
+        <v>17.2902</v>
       </c>
       <c r="D19" t="n">
-        <v>24.32094</v>
+        <v>16.56878</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.2655</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.36651</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05077</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.80702</v>
       </c>
     </row>
     <row r="20">
@@ -742,10 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.81315</v>
+        <v>17.17437</v>
       </c>
       <c r="D20" t="n">
-        <v>24.25976</v>
+        <v>16.87012</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.03065</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.24017</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81203</v>
       </c>
     </row>
     <row r="21">
@@ -769,16 +961,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -788,26 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.89424</v>
+        <v>15.87738</v>
       </c>
       <c r="D22" t="n">
-        <v>16.73592</v>
+        <v>15.68347</v>
       </c>
       <c r="E22" t="n">
-        <v>16.73407</v>
+        <v>15.82143</v>
       </c>
       <c r="F22" t="n">
-        <v>43.43821</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05085</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.8601</v>
+        <v>252.58712</v>
       </c>
     </row>
     <row r="23">
@@ -817,22 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.98439</v>
+        <v>16.19417</v>
       </c>
       <c r="D23" t="n">
-        <v>16.98635</v>
+        <v>15.63016</v>
       </c>
       <c r="E23" t="n">
-        <v>16.99067</v>
+        <v>15.69855</v>
       </c>
       <c r="F23" t="n">
-        <v>42.62137</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05063</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.84536</v>
+        <v>254.93538</v>
       </c>
     </row>
     <row r="24">
@@ -842,22 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.92951</v>
+        <v>16.02189</v>
       </c>
       <c r="D24" t="n">
-        <v>16.95051</v>
+        <v>15.78421</v>
       </c>
       <c r="E24" t="n">
-        <v>16.97272</v>
+        <v>15.955</v>
       </c>
       <c r="F24" t="n">
-        <v>44.49812</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05094</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.8274</v>
+        <v>260.12954</v>
       </c>
     </row>
     <row r="25">
@@ -867,22 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17.18863</v>
+        <v>16.06798</v>
       </c>
       <c r="D25" t="n">
-        <v>16.55494</v>
+        <v>15.66102</v>
       </c>
       <c r="E25" t="n">
-        <v>17.21775</v>
+        <v>15.75763</v>
       </c>
       <c r="F25" t="n">
-        <v>43.07224</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.04999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.84174</v>
+        <v>254.12456</v>
       </c>
     </row>
     <row r="26">
@@ -892,22 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.73615</v>
+        <v>16.01762</v>
       </c>
       <c r="D26" t="n">
-        <v>16.73888</v>
+        <v>15.8777</v>
       </c>
       <c r="E26" t="n">
-        <v>16.92653</v>
+        <v>15.89829</v>
       </c>
       <c r="F26" t="n">
-        <v>43.9208</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05071</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.87153</v>
+        <v>257.42797</v>
       </c>
     </row>
     <row r="27">
@@ -917,22 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.85428</v>
+        <v>16.14228</v>
       </c>
       <c r="D27" t="n">
-        <v>17.03992</v>
+        <v>15.70084</v>
       </c>
       <c r="E27" t="n">
-        <v>16.98977</v>
+        <v>15.70366</v>
       </c>
       <c r="F27" t="n">
-        <v>43.25997</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05124</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.83219</v>
+        <v>255.17935</v>
       </c>
     </row>
     <row r="28">
@@ -942,22 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.18336</v>
+        <v>16.12131</v>
       </c>
       <c r="D28" t="n">
-        <v>16.60379</v>
+        <v>15.96273</v>
       </c>
       <c r="E28" t="n">
-        <v>16.99564</v>
+        <v>15.96722</v>
       </c>
       <c r="F28" t="n">
-        <v>42.84008</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.87122</v>
+        <v>251.72654</v>
       </c>
     </row>
     <row r="29">
@@ -967,22 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.14814</v>
+        <v>15.59746</v>
       </c>
       <c r="D29" t="n">
-        <v>16.71155</v>
+        <v>15.49611</v>
       </c>
       <c r="E29" t="n">
-        <v>16.49207</v>
+        <v>15.54297</v>
       </c>
       <c r="F29" t="n">
-        <v>42.44704</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05182</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.87603</v>
+        <v>254.28128</v>
       </c>
     </row>
     <row r="30">
@@ -992,22 +1126,744 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.98332</v>
+        <v>16.10647</v>
       </c>
       <c r="D30" t="n">
-        <v>17.20665</v>
+        <v>15.77997</v>
       </c>
       <c r="E30" t="n">
-        <v>16.94582</v>
+        <v>16.08282</v>
       </c>
       <c r="F30" t="n">
-        <v>43.64268</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05119</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.88056</v>
+        <v>255.00109</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.85138</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.9209</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.73706</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.18661</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.55507</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.66596</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.82847</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.19892</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.40089</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.37408</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.12529</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.95357</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.56685</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.08359</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.41748</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.04445</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.40688</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.75754</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.82642</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.85852</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.72475</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.34006</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.59993</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.92246</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.10249</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.25379</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.32616</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.62061</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.66402</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.9746</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.2976</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.63043</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.17596</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35.2095</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.86477</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.02809</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.45517</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.83723</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.2786</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.08636</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.07216</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.3969</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.60163</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.43122</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.71765</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.04807</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.46804</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.10541</v>
+      </c>
+      <c r="G42" t="n">
+        <v>35.32139</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.64665</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.10981</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.45365</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.04605</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.5622</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.97254</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.93261</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.32112</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.22974</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.20394</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.9401</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.2446</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.79513</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.67428</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.7655</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.92004</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.15765</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.42481</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.06406</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.87842</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.00468</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.9049</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.8454</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.96919</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.4906</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.84968</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.32822</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.54338</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.65418</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.58938</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.19987</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.43177</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.59213</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.78661</v>
+      </c>
+      <c r="G49" t="n">
+        <v>35.19239</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.67949</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.19239</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.59728</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.40342</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.60879</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.61892</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.12509</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.61199</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.13253</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.61899</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.1368</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.61452</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.14663</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61451</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.135</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6049099999999999</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.12011</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61314</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.11286</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60263</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.13296</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.61103</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.12566</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.60966</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.12482</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.61481</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.1426</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.62115</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.14059</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.61434</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.12982</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.61333</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.11348</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60946</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.13962</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.6121</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.109</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.11025</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60647</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.12094</v>
       </c>
     </row>
   </sheetData>
